--- a/SINGLE HADITH CONTENT/missing_input/[V1] UPODESH-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] UPODESH-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,6 +1003,397 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>عَنْ عُقْبَةَ بْنِ عَامِرٍ يَقُولُ سَمِعْتُ رَسُوْلَ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم يَقُوْلُ مَنْ تَعَلَّقَ تَمِيْمَةً فَلاَ أَتَمَّ اللهُ لَهُ وَمَنْ تَعَلَّقَ وَدَعَةً فَلاَ وَدَعَ اللهُ لَهُ.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘যে ব্যক্তি তা‘বীয ব্যবহার করবে আল্লাহ তাকে পূর্ণতা দিবেন না। আর যে কড়ি ব্যবহার করবে আল্লাহ তাকে মঙ্গল দান করবেন না’ (আহমাদ হা/১৬৭৬৩, হাদীছ ছহীহ)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>عَنْ عُقْبَةَ بْنِ عَامِرٍ الْجُهَنِيِّ أَنَّ رَسُوْلَ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم أَقْبَلَ إِلَيْهِ رَهْطٌ فَبَايَعَ تِسْعَةً وَأَمْسَكَ عَنْ وَاحِدٍ فَقَالُوْا يَا رَسُوْلَ اللهِ بَايَعْتَ تِسْعَةً وَتَرَكْتَ هَذَا قَالَ إِنَّ عَلَيْهِ تَمِيْمَةً فَأَدْخَلَ يَدَهُ فَقَطَعَهَا فَبَايَعَهُ وَقَالَ مَنْ عَلَّقَ تَمِيمَةً فَقَدْ أَشْرَكَ-</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর খিদমতে একদল লোক উপস্থিত হল। অতঃপর রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দলটির ৯ জনকে বায়‘আত করালেন এবং একজনকে বায়‘আত করালেন না। তারা বলল, হে আল্লাহর রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)! আপনি ৯ জনকে বায়‘আত করালেন আর একজনকে ছেড়ে দিলেন? রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, ‘তার সাথে একটি তা‘বীয রয়েছে’। তখন লোকটি হাত ভিতরে ঢুকিয়ে তা‘বীয ছিড়ে ফেললেন। অতঃপর রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকেও বায়‘আত করালেন এবং বললেন, যে ব্যক্তি তা‘বীয ব্যবহার করল সে শির্ক করল’ (আহমাদ হা/১৬৭৭১, হাদীছ ছহীহ)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>عَنْ رُوَيْفَعَ بْنَ ثَابِتٍ يَقُولُ إِنَّ رَسُوْلَ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم قَالَ يَا رُوَيْفِعُ لَعَلَّ الْحَيَاةَ سَتَطُوْلُ بِكَ بَعْدِيْ فَأَخْبِرْ النَّاسَ أَنَّهُ مَنْ عَقَدَ لِحْيَتَهُ أَوْ تَقَلَّدَ وَتَرًا أَوْ اسْتَنْجَى بِرَجِيعِ دَابَّةٍ أَوْ عَظْمٍ فَإِنَّ مُحَمَّدًا بَرِيءٌ مِنْهُ إِنَّ الرُّقَى وَالتَّمَائِمَ وَالتِّوَلَةَ شِرْكٌ-</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, ‘হে রুওয়াইফা! হয়তো তুমি আমার পরেও অনেক দিন বেঁচে থাকবে। সুতরাং তুমি লোকদেরকে এ কথা বলে দিও যে, যে ব্যক্তি দাড়িতে গিট দিল অথবা তা‘বীয জাতীয় বেল্ট বা সুতা (ছেলে-মেয়ের বা প্রাণীর গলায়) পরাল কিংবা চতুষ্পদ জন্তুর গোবর অথবা হাড় দিয়ে ইসতেঞ্জা করল, নিশ্চয়ই তার সাথে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোন সম্পর্ক নেই’ (আবূদাঊদ, মিশকাত হা/৩৫১ সনদ ছহীহ, বাংলা মিশকাত ২য় খণ্ড, হা/৩২৪ ‘পেশাব-পায়খানার শিষ্টাচার’ অনুচ্ছেদ)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>عَنْ مُجَاهِدٍ قَالَ كُنَّا مَعَ ابْنِ عُمَرَ فِيْ سَفَرٍ، فَمَرَّ بِمَكَانٍ فَحَادَ عَنْهُ، فَسُئِلَ لِمَ فَعَلْتَ؟ فَقَالَ رَأَيْتُ رَسُوْلَ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم فَعَلَ هَذَا فَفَعَلْتُ.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>আমরা একদা এক সফরে ইবনু ওমরের সাথে ছিলাম। তিনি এক স্থান দিয়ে পার হওয়ার সময় একটু জায়গা রাস্তা থেকে সরে পার হলেন। তাকে জিজ্ঞেস করা হল- আপনি কেন এরূপ করলেন? তিনি বললেন, আমি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এই স্থানে এরূপ করতে দেখেছি, তাই আমি করলাম’ (আহমাদ হা/৪৮৭০; তারগীব হা/৭০)। একেই অনুসরণ বলে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ بَرْزَةَ رَضِيَ اللهُ عَنْهُ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم إِنَّمَا أَخْشَى عَلَيْكُمْ شَهَوَاتِ الْغَيِّ فِيْ بُطُوْنِكُمْ وَفُرُوْجِكُمْ وَمُضِلَّاتِ الْهَوَى.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>নবী কারীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘নিশ্চয়ই আমি তোমাদের ব্যাপারে তোমাদের অবৈধ উপার্জনের প্রবৃত্তি এবং অশ্লীল কাজে লিপ্ত হওয়ার প্রবৃত্তি সম্পর্কে ভয় করি এবং প্রবৃত্তির অনুসরণ করে সুন্নাতের ব্যাপারে ভ্রান্ত পথে চলার আশংকা করি’ (মুসনাদু বাযযার হা/৩৮৪৪; আত-তারগীব হা/৭৭)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ هُرَيْرَةَ قَالَ سُئِلَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم عَنْ أَكْثَرِ مَا يُدْخِلُ النَّاسَ الْجَنَّةَ فَقَالَ تَقْوَى اللهِ وَحُسْنُ الْخُلُقِ وَسُئِلَ عَنْ أَكْثَرِ مَا يُدْخِلُ النَّاسَ النَّارَ فَقَالَ الْفَمُ وَالْفَرْجُ-</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হল, কোন জিনিস মানুষকে সবচেয়ে বেশী জান্নাতে প্রবেশ করাবে? তিনি বলেন, তা হচ্ছে- আল্লাহভীতি ও উত্তম চরিত্র। আর জিজ্ঞেস করা হল, মানুষকে কোন জিনিস সবচেয়ে বেশী জাহান্নামে প্রবেশ করাবে? তিনি বললেন, তা হচ্ছে- মুখ বা জিহ্বা ও অপরটি লজ্জাস্থান’ (তিরমিযী, বঙ্গানুবাদ মিশকাত হা/৪৬২১, হাদীছ ছহীহ)। অত্র হাদীছ দ্বারা বুঝা যায় যে, মানুষকে জাহান্নামে প্রবেশ করানোর সবচেয়ে বড় মাধ্যম হচ্ছে জিহ্বা। কারণ জিহ্বা দ্বারা মানুষ সত্যকে মিথ্যা ও মিথ্যাকে সত্যে পরিণত করতে পারে। এর কারণে মানুষ ক্ষতিগ্রস্ত হয়। সমাজে বিশৃংখলা, অশান্তি, অরাজকতা ও নৈরাজ্য নেমে আসে। এজন্য জিহ্বা নিয়ন্ত্রণ করা যরূরী।</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>عَنْ سَهْلِ بْنِ سَعْدٍ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم مَنْ يَضْمَنْ لِيْ مَا بَيْنَ لَحْيَيْهِ وَمَا بَيْنَ رِجْلَيْهِ أَضْمَنْ لَهُ الْجَنَّةَ-</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘যে ব্যক্তি আমার কাছে (এই অঙ্গীকার করবে যে, সে) তার দুই চোয়ালের মধ্যস্থিত বস্তুর এবং তার দু’পায়ের মধ্যস্থিত বস্তুর যিম্মাদার হবে তবে আমি তার জন্য জান্নাতের যিম্মাদার হব’ (বুখারী, বঙ্গানুবাদ মিশকাত হা/৪৬০১)। অর্থাৎ যে ব্যক্তি তার জিহ্বা ও লজ্জাস্থানের হেফাযত করবে, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তার জন্য জান্নাতের যিম্মাদার হবেন। কারণ লজ্জাস্থান হচ্ছে সমাজে অশ্লীলতা বিস্তারের মাধ্যম। এর কারণে মানুষ অপমানিত ও লাঞ্ছিত হয়। এসব থেকে বেঁচে থাকার জন্য লজ্জাস্থানের হেফাযত করা আবশ্যক।</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ هُرَيْرَةَ رَضِيَ اللهُ عَنْهُ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم تَجِدُوْنَ شَرَّ النَّاسِ ذَا الْوَجْهَيْنِ الَّذِيْ يَأْتِيْ هَؤُلاَءِ بِوَجْهٍ وَيَأْتِيْ هَؤُلاَءِ بِوَجْهٍ-</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘তোমরা ক্বিয়ামতের দিন সর্বাপেক্ষা মন্দ লোক ঐ ব্যক্তিকে পাবে, যে দ্বিমুখী। সে এক মুখ নিয়ে এদের কাছে আসে এবং আরেক মুখ নিয়ে তাদের কাছে যায়’ (বুখারী, মুসলিম, মিশকাত হা/৪৮২২; বাংলা মিশকাত ৯ম খণ্ড, হা/৪৬১১)। অত্র হাদীছ দু’টি হতে প্রতীয়মান হয় যে, মানুষের জিহ্বা ও লজ্জাস্থান কবীরা গুনাহ সমূহের উৎস। কেননা মানুষ মুখ দ্বারা মিথ্যাচার, গালমন্দ, চোগলখুরী, ধোঁকাবাজি, গীবত-তোহমত, অভিসম্পাৎ প্রভৃতি কবীরা গোনাহ করে থাকে। কিন্তু মানুষ এসব পাপ থেকে সাবধান হওয়ার ন্যূনতম চেষ্টা করে না। এগুলি থেকে বেঁচে থাকার জন্য আমাদের জিহ্বাকে সংবরণ করা অত্যাবশ্যক। কেননা এগুলির ব্যাপারে কঠিন হুঁশিয়ারী উচ্চারণ করে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেন, ‘চোগলখোর ও খোটাদানকারী জান্নাতে প্রবেশ করবে না’ (বুখারী, মুসলিম, বাংলা মিশকাত হা/৪৬১২)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ الدَّرْدَاءِ قَالَ سَمِعْتُ رَسُوْلَ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم يَقُوْلُ إِنَّ اللَّعَّانِيْنَ لاَ يَكُونُوْنَ شُهَدَاءَ وَلاَ شُفَعَاءَ يَوْمَ الْقِيَامَةِ-</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে আমি বলতে শুনেছি, ‘নিশ্চয়ই অভিশাপকারী কখনো ক্বিয়ামতের মাঠে সাক্ষী ও সুপারিশকারী হতে পারবে না’ (মুসলিম, মিশকাত হা/৪৮২০; বাংলা মিশকাত ৯ম খণ্ড, হা/৪৬০৯)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ هُرَيْرَةَ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم إِنَّ الْعَبْدَ لَيَتَكَلَّمُ بِالْكَلِمَةِ مِنْ رِضْوَانِ اللهِ لَا يُلْقِيْ لَهَا بَالاً يَرْفَعُهُ اللهُ بِهَا دَرَجَاتٍ وَإِنَّ الْعَبْدَ لَيَتَكَلَّمُ بِالْكَلِمَةِ مِنْ سَخَطِ اللهِ لَا يُلْقِي لَهَا بَالًا يَهْوِيْ بِهَا فِيْ جَهَنَّمَ، وَفِيْ رِوَايَةٍ لَهُمَا يَهْوِيْ بِهَا فِي النَّارِ أَبْعَدَ مَا بَيْنَ الْمَشْرِقِ وَالْمَغْرِبِ-</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘নিশ্চয়ই বান্দা কখনও এমন কথা বলে যাতে আল্লাহর সন্তুষ্টি বিদ্যমান। অথচ সে তার গুরুত্ব জানে না। আল্লাহ এর দ্বারা তার মর্যাদা বৃদ্ধি করে দেন। পক্ষান্তরে বান্দা এমন কথা বলে, যাতে আল্লাহর অসন্তুষ্টি বিদ্যমান। অথচ সে তার অনিষ্ট সম্পর্কে অবগত নয়। আর এ কথাই তাকে জাহান্নামে নিক্ষেপ করে। বুখারী ও মুসলিমের অন্য এক বর্ণনায় আছে যে, এই কথাই তাকে জাহান্নামের এত গভীরে পৌঁছে দেয়, যার পরিধি পূর্ব ও পশ্চিমের দূরত্ব পরিমাণ’ (বুখারী, মিশকাত হা/৪৮১৩; বাংলা মিশকাত ৯ম খণ্ড, হা/৪৬০২ ‘শিষ্টাচার’ অধ্যায়)। উল্লিখিত হাদীছ সমূহ দ্বারা বুঝা যায় যে, মানুষের যবান সাংঘাতিক জিনিস, যা মানুষকে জান্নাতের উচ্চ শিখরে পৌঁছে দেয়, আবার জাহান্নামের গভীর গহ্বরেও নিক্ষেপ করে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>عَنْ عَبْدِ اللهِ بْنِ مَسْعُوْدٍ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم إِنَّ الصِّدْقَ بِرٌّ وَإِنَّ الْبِرَّ يَهْدِيْ إِلَى الْجَنَّةِ وَإِنَّ الْعَبْدَ لَيَتَحَرَّى الصِّدْقَ حَتَّى يُكْتَبَ عِنْدَ اللهِ صِدِّيقًا وَإِنَّ الْكَذِبَ فُجُورٌ وَإِنَّ الْفُجُوْرَ يَهْدِيْ إِلَى النَّارِ وَإِنَّ الْعَبْدَ لَيَتَحَرَّى الْكَذِبَ حَتَّى يُكْتَبَ كَذَّابًا-</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘নিশ্চয়ই সত্যবাদিতা একটি পুণ্যময় কাজ। আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সর্বদা সত্যের উপর দৃঢ় থাকে তাকে আল্লাহর খাতায় সত্যনিষ্ঠ বলে লিখে নেয়া হয়। পক্ষান্তরে মিথ্যা হচ্ছে পাপকাজ। পাপাচার জাহান্নামের পথ দেখায়। যে ব্যক্তি সদা মিথ্যা কথা বলে এবং মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর খাতায় মিথ্যুক বলে লিখে নেয়া হয়’ (বুখারী, মুসলিম, বাংলা মিশকাত ৯ম খণ্ড হা/৪৬১৩)। তাই আমাদের সকলের উচিত কথা বলার পূর্বে চিন্তা-ভাবনা করে বলা এবং আল্লাহর সন্তুষ্টিপূর্ণ কথা বলার চেষ্টা করা। যাতে আল্লাহর অসন্তোষ রয়েছে, সেসব কথা বলা থেকে বিরত থাকা। অনুরূপভাবে সত্য বলার চেষ্টা করা এবং মিথ্যা বলা থেকে বেঁচে থাকা। সেই সাথে আল্লাহর যিকরে মশগূল থাকা। আল্লাহর বাণী ‘নিশ্চয়ই যে সকল নারী-পুরুষ বেশী বেশী আল্লাহকে স্মরণ করে আল্লাহ তাদের জন্য মাগফিরাত ও মহা প্রতিদান প্রস্তুত করে রেখেছেন’ (আহযাব ৩৫)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>عَنْ حُذَيْفَةَ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم لَا يَدْخُلُ الْجَنَّةَ قَتَّاتٌ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>আমি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে বলতে শুনেছি, ‘চোগলখোর জান্নাতে প্রবেশ করবে না’ (মুত্তাফাক্ব আলাইহ, বাংলা মিশকাত হা/৪৬১২)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ هُرَيْرَةَ قَالَ قِيْلَ يَا رَسُوْلَ اللهِ مَا الْغِيْبَةُ قَالَ ذِكْرُكَ أَخَاكَ بِمَا يَكْرَهُ قَالَ أَرَأَيْتَ إِنْ كَانَ فِيْهِ مَا أَقُوْلُ قَالَ إِنْ كَانَ فِيْهِ مَا تَقُوْلُ فَقَدْ اغْتَبْتَهُ وَإِنْ لَمْ يَكُنْ فِيْهِ مَا تَقُوْلُ فَقَدْ بَهَتَّهُ-</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, একদা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জিজ্ঞেস করলেন, ‘তোমরা কি জান গীবত কি’? তাঁরা বললেন, আল্লাহ ও তাঁর রাসূল অধিক জানেন। তিনি বললেন, ‘তোমার কোন ভাই সম্পর্কে এমন কথা বল, যা সে অপসন্দ করে’। জিজ্ঞেস করা হল, আমি যা বলি যদি তা আমার ভাইয়ের মধ্যে বিদ্যমান থাকে, তাহলে আপনার কি অভিমত? তখন তিনি বললেন, ‘তুমি যা বল তার মধ্যে তা থাকলে তুমি তার গীবত করলে। আর যদি তার মধ্যে তা না থাকে যা তুমি বল, তখন তুমি তার প্রতি মিথ্যা অপবাদ আরোপ করলে’ (মুসলিম, বাংলা মিশকাত হা/৪৬১৭)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>عَنْ عَائِشَةَ قَالَتْ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم إِنَّ شَرَّ النَّاسِ عِنْدَ اللهِ مَنْزِلَةً يَوْمَ الْقِيَامَةِ مَنْ تَرَكَهُ النَّاسُ اتِّقَاءَ شَرِّهِ، وفي رواية إتِّقَاءَ فَحْشِهِ-</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘ক্বিয়ামতের দিন আল্লাহর নিকট মর্যাদায় সেই ব্যক্তিই মন্দ বলে সাব্যস্ত হবে, যার অনিষ্টের ভয়ে লোকেরা তাকে ত্যাগ করেছে’। অপর এক বর্ণনায় আছে, ‘যার অশ্লীলতার ভয়ে লোকেরা তাকে পরিত্যাগ করেছে’ (বুখারী, মুসলিম, বাংলা মিশকাত হা/৪৬১৮)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>عَنْ عُقْبَةَ بْنِ عَامِرٍ رَضِيَ اللهُ عَنْهُ قَالَ قُلْتُ يَا رَسُوْلَ اللهِ مَا النَّجَاةُ قَالَ أَمْسِكْ عَلَيْكَ لِسَانَكَ وَلْيَسَعْكَ بَيْتُكَ وَابْكِ عَلَى خَطِيئَتِكَ-</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>একদা আমি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে সাক্ষাৎ করলাম এবং বললাম, নাজাতের উপায় কি? তিনি বললেন, ‘নিজের জিহ্বা আয়ত্তে রাখ, নিজের ঘরে পড়ে থাক এবং নিজের পাপের জন্য রোদন কর’ (আহমাদ, তিরমিযী, মিশকাত হা/৪৮৩৭; বাংলা মিশকাত হা/৪৬২৬, সনদ হাসান)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>عَنْ عَمَّارِ بْنِ يَاسِرٍ رَضِيَ اللهُ عَنْهُ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم مَنْ كَانَ ذَا وَجْهَيْنِ فِي الدُّنْيَا كَانَ لَهُ لِسَانَانِ مِنْ نَارٍ يَوْمَ الْقِيَامَةِ-</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘যে ব্যক্তি দুনিয়াতে দ্বিমুখী, ক্বিয়ামতের দিন তার (মুখে) আগুনের দু’টি জিহ্বা হবে’ (দারেমী, মিশকাত হা/৪৮৪৬; বাংলা মিশকাত হা/৪৬৩৩, সনদ হাসান)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>عَنْ عَبْدِ اللهِ رَضِيَ اللهُ عَنْهُ قَالَ قَالَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم لَيْسَ الْمُؤْمِنُ بِالطَّعَّانِ وَلَا بِاللَّعَّانِ وَلَا الْفَاحِشِ وَلَا الْبَذِيْءِ-</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘মুমিন ব্যক্তি ভর্ৎসনাকারী, অভিসম্পাৎকারী, অশ্লীল গালমন্দকারী ও নির্লজ্জ হতে পারে না’ (তিরমিযী, বায়হাক্বী, মিশকাত হা/৪৮৪৭; বাংলা মিশকাত হা/৪৬৩৪, সনদ ছহীহ)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>عَنْ عَائِشَةَ رَضِيَ اللهُ عَنْهَا قَالَتْ قُلْتُ لِلنَّبِيِّ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم حَسْبُكَ مِنْ صَفِيَّةَ كَذَا وَكَذَا تَعْنِيْ قَصِيْرَةً فَقَالَ لَقَدْ قُلْتِ كَلِمَةً لَوْ مُزِجَتْ بِهَا الْبَحْرَ لَمَزِجَتْهُ-</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, আমি নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে বললাম, ছাফিয়্যা সম্পর্কে আপনাকে এইটুকু বলাই যথেষ্ট যে, সে এইরূপ এইরূপ। তিনি এটা দ্বারা বুঝাতে চাইলেন যে, তিনি বেঁটে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, ‘যদি তোমার এ কথাকে সমুদ্রের সাথে মিশিয়ে দেওয়া হয়, তবে তা সমুদ্রের রং পরিবর্তন করে দেবে’ (আহমাদ, তিরমিযী, আবুদাউদ, মিশকাত হা/৪৮৫৩; বাংলা মিশকাত হা/৪৬৪০, সনদ ছহীহ)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>عَنْ عُبَادَةَ بْنِ الصَّامِتِ رَضِيَ اللهُ عَنْهُ قَالَ قَالَ رَسُوْلُ الله صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم اضْمَنُوْا لِيْ سِتًّا مِنْ أَنْفُسِكُمْ، أَضْمَنْ لَكُمُ الْجَنَّةَ اُصْدُقُوْا إِذَا حَدَّثْتُمْ، وَأَوْفُوْا إِذَا وَعَدْتُمْ، وَأَدُّوْا إِذَا ائْتُمِنْتُمْ، وَاحْفَظُوْا فُرُوْجَكُمْ، وَغُضُّوْا أَبْصَارَكُمْ، وَكُفُّوْا أَيْدِيَكُمْ.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘তোমরা নিজেদের পক্ষ হতে আমাকে ছয়টি বিষয়ের জামানত দাও, আমি তোমাদের জন্য জান্নাতের যামিন হব। (১) তোমরা যখন কথাবার্তা বল, তখন সত্য বলবে। (২) যখন ওয়াদা কর, তা পূর্ণ করবে। (৩) যখন তোমাদের কাছে আমানত রাখা হয়, তা আদায় করবে। (৪) নিজেদের লজ্জাস্থানকে হেফাযত করবে। (৫) স্বীয় দৃষ্টিকে অবনমিত রাখবে এবং (৬) স্বীয় হস্তকে (অন্যায় কাজ হতে) বিরত রাখবে’ (আহমাদ, বায়হাক্বী, মিশকাত হা/৪৮৭০; বাংলা মিশকাত হা/৪৬৫৬, সনদ হাসান)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>عَنْ أَبِيْ هُرَيْرَةَ رَضِيَ اللهُ عَنْهُ قَالَ قَالَ رَسُوْلُ الله صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم إيَّاكُمْ وَالظَّنَّ، فَإنَّ الظَّنَّ أَكْذَبُ الحَدِيْثِ، وَلاَ تَحَسَّسُوْا، وَلاَ تَجَسَّسُوْا، وَلاَ تَنَاجَشُوْا، وَلاَ تَحَاسَدُوْا، وَلاَ تَبَاغَضُوْا، وَلاَ تَدَابَرُوْا وَكُوْنُوْا عِبَادَ الله إِخْوَانًا.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কারো সম্পর্কে (মন্দ) ধারণা হতে বেঁচে থাক। কেননা ধারণা বড় ধরনের মিথ্যা। কারো কোন দোষের কথা জানতে চেষ্টা কর না। গোয়েন্দাগিরি কর না, ক্রয়-বিক্রয়ে ধোঁকাবাজি কর না, পরস্পর হিংসা রেখ না, পরস্পর শত্রুতা কর না এবং একে অন্যের পিছনে লেগ না। বরং পরস্পর এক আল্লাহর বান্দা ও ভাই ভাই হয়ে থাক। অপর এক বর্ণনায় আছে, ‘পরস্পর লোভ-লালসা কর না’। (মুত্তাফাক্ব আলাইহ, বাংলা মিশকাত হা/৪৮০৮)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>عَنْ ابْنِ عُمَرَ رَضِيَ اللهُ عَنْهُ قَالَ صَعِدَ رَسُوْلُ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم الْمِنْبَرَ فَنَادَى بِصَوْتٍ رَفِيعٍ فَقَالَ يَا مَعْشَرَ مَنْ أَسْلَمَ بِلِسَانِهِ وَلَمْ يُفْضِ الْإِيْمَانُ إِلَى قَلْبِهِ، لاَ تُؤْذُوْا الْمُسْلِمِيْنَ وَلاَ تُعَيِّرُوْهُمْ وَلاَ تَتَّبِعُوْا عَوْرَاتِهِمْ، فَإِنَّهَ مَنْ تَتَبَّعَ عَوْرَةَ أَخِيْهِ اَلْمُسْلِمِ تَتَبَّعَ اللهُ عَوْرَتَهُ، وَمَنْ تَتَبَّعَ اللهُ عَوْرَتَهُ يَفْضَحْهُ وَلَوْ فِىْ جَوْفِ رَحْلِهِ.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, একদা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মিম্বরে আরোহন করে উচ্চৈঃস্বরে বললেন, ‘হে ঐ সকল লোক! যারা মুখে ইসলাম গ্রহণ করেছে, কিন্তু ঈমান তাদের অন্তরে প্রোথিত হয়নি, তোমরা মুসলমানদেরকে কষ্ট দিয়ো না, তাদেরকে ভর্ৎসনা কর না এবং তাদের দোষ-ত্রুটি অনুসন্ধান কর না। কেননা যে তার মুসলিম ভাইয়ের দোষ-ত্রুটি অনুসন্ধান করে বেড়ায়, আল্লাহ তার দোষ-ত্রুটি অনুসন্ধান করবেন। আর আল্লাহ যার দোষ-ত্রুটি অনুসন্ধান করবেন, তাকে অপদস্থ করবেন, সে তার বাহনের পেটের মধ্যে অবস্থান করলেও’ (তিরমিযী হা/২০৩২, হাদীছ হাসান, ‘মুমিনকে সম্মান করা’ অনুচ্ছেদ; বাংলা মিশকাত হা/৪৮২৩)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>عَنْ أَنَسٍ رَضِيَ اللهُ عَنْهُ قَالَ : قَالَ رَسُوْلُ الله صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم لَمَّا عُرِجَ بِيْ رَبِّيْ مَرَرْتُ بِقَوْمٍ لَهُمْ أظْفَارٌ مِنْ نُحَاسٍ يَخْمِشُوْنَ وُجُوْهَهُمْ وَصُدُوْرَهُمْ فَقُلْتُ مَنْ هؤُلاَءِ يَا جِبْرِيْلُ؟ قَالَ هؤُلاَءِ الَّذِيْنَ يَأكُلُوْنَ لُحُوْمَ النَّاسِ وَيَقَعُوْنَ فِيْ أعْرَاضِهِمْ-</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘আমার পরওয়ারদেগার যখন আমাকে মি‘রাজে নিয়ে গেলেন, তখন আমি কতিপয় লোকের নিকট দিয়ে গমন করলাম, যাদের নখ ছিল তামার। তা দ্বারা তারা নিজেদের মুখমণ্ডল ও বক্ষ আঁচড়াতে ছিল। আমি জিজ্ঞেস করলাম, হে জিবরাঈল! এরা কারা? তিনি বললেন, ঐ সকল লোক যারা মানুষের গোশত খেত এবং তাদের ইযযত আব্রুর হানি করত’ (আবুদাউদ, বাংলা মিশকাত হা/৪৮২৫)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>عَنْ عَائِشَةَ رَضِيَ اللهُ عَنْهَا أَنَّ رَسُوْلَ اللهِ صَلَّى اللّٰهُ عَلَيْهِ وَسَلَّم قَالَ: إِنَّ اللهَ تَعَالَى رَفِيْقٌ يُحِبُّ الرِّفْقَ وَيُعْطِيْ عَلَى الرِّفْقِ مَا لَا يُعْطِيْ عَلَى الْعُنْفِ وَمَا لَا يُعْطِي عَلَى مَا سِوَاهُ. وَفِي رِوَايَةٍ لَهُ: قَالَ لِعَائِشَةَ: عَلَيْكِ بِالرِّفْقِ وَإِيَّاكِ وَالْعُنْفَ وَالْفُحْشَ إِنَّ الرِّفْقَ لَا يَكُوْنُ فِيْ شَيْءٍ إِلَّا زَانَهُ وَلَا يُنْزَعُ مِنْ شَيْء إِلَّا شَانَهُ.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, ‘আল্লাহ কোমল, তিনি কোমলতাকে ভালবাসেন। আর তিনি কোমলতার প্রতি যত অনুগ্রহ করেন, কঠোরতা এবং অন্য কোন আচরণের প্রতি তত অনুগ্রহ করেন না’। মুসলিমের অপর এক বর্ণনায় আছে, একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) আয়েশা (রাঃ)-কে বলেন, ‘কোমলতা নিজের জন্য বাধ্যতামূলক করে নাও এবং কঠোরতা ও নির্লজ্জতা হতে নিজেকে বাঁচাও। কারণ যাতে নম্রতা ও কোমলতা থাকে তার সৌন্দর্য বৃদ্ধি হয়। আর যাতে কোমলতা থাকে না, তা দোষণীয় হয়ে পড়ে’ (মুসলিম, মিশকাত হা/৫০৬৮)।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
